--- a/tables/Table S9.xlsx
+++ b/tables/Table S9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michael.studivan/Documents/GitHub/PortMiami-urban-coral-resilience/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6C18382-889F-9844-93E5-AD81CC827BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95260E0A-3F5D-1B47-89E5-CBBC92154B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="3880" windowWidth="26440" windowHeight="15180" xr2:uid="{1362957D-6C46-C04B-801F-B184BCDA2A63}"/>
+    <workbookView xWindow="6780" yWindow="3880" windowWidth="26440" windowHeight="15180" xr2:uid="{89A9F25D-FA09-224B-BFF8-AFA61B16EA13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,180 +36,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="39">
   <si>
     <t>Species</t>
   </si>
   <si>
-    <t>Module</t>
+    <t>Comparison</t>
+  </si>
+  <si>
+    <t>Stress Family</t>
   </si>
   <si>
     <t>Gene ID</t>
   </si>
   <si>
-    <t>InterPro ID</t>
-  </si>
-  <si>
-    <t>Positive Correlations</t>
-  </si>
-  <si>
-    <t>Negative Correlations</t>
-  </si>
-  <si>
-    <t>Gene annotation [InterPro annotation]</t>
+    <t>Gene Annotation</t>
+  </si>
+  <si>
+    <t>Up In</t>
+  </si>
+  <si>
+    <t>Down In</t>
   </si>
   <si>
     <t>Orbicella faveolata</t>
   </si>
   <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>Ofaveolata017749</t>
-  </si>
-  <si>
-    <t>Emerald Reef, Bleaching, Growth Rate, Temperature</t>
-  </si>
-  <si>
-    <t>MacArthur North, Genotype, Fv/Fm, Fv/Fm Ratio, Survival, Durusdinium, pH</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>blue</t>
-  </si>
-  <si>
-    <t>Ofaveolata015137</t>
-  </si>
-  <si>
-    <t>IPR008937</t>
-  </si>
-  <si>
-    <t>Rainbow Reef</t>
-  </si>
-  <si>
-    <t>Guanine nucleotide exchange factor for Ras-like GTPases; N-terminal motif [Ras-like guanine nucleotide exchange factor]</t>
-  </si>
-  <si>
-    <t>brown</t>
-  </si>
-  <si>
-    <t>Ofaveolata002622</t>
-  </si>
-  <si>
-    <t>IPR001019</t>
-  </si>
-  <si>
-    <t>Bleaching, Temperature</t>
-  </si>
-  <si>
-    <t>Type 2A serotonin receptor binding [Guanine nucleotide binding protein (G-protein), alpha subunit]</t>
-  </si>
-  <si>
-    <t>cyan</t>
-  </si>
-  <si>
-    <t>Ofaveolata031334</t>
-  </si>
-  <si>
-    <t>IPR002227</t>
-  </si>
-  <si>
-    <t>MacArthur North, Genotype, Fv/Fm, Fv/Fm Ratio, Survival, Durusdinium</t>
-  </si>
-  <si>
-    <t>Emerald Reef, Rainbow Reef, Growth Rate, Breviolum</t>
-  </si>
-  <si>
-    <t>Common central domain of tyrosinase [Tyrosinase copper-binding domain]</t>
-  </si>
-  <si>
-    <t>grey60</t>
-  </si>
-  <si>
-    <t>Ofaveolata030647</t>
-  </si>
-  <si>
-    <t>IPR051882</t>
-  </si>
-  <si>
-    <t>Sequence-specific DNA binding [ATF basic-leucine zipper (bZIP) transcription factors]</t>
-  </si>
-  <si>
-    <t>magenta</t>
-  </si>
-  <si>
-    <t>Ofaveolata007974</t>
-  </si>
-  <si>
-    <t>midnightblue</t>
-  </si>
-  <si>
-    <t>Ofaveolata008780</t>
-  </si>
-  <si>
-    <t>IPR004539</t>
-  </si>
-  <si>
-    <t>pH</t>
-  </si>
-  <si>
-    <t>Translation elongation factor activity [Translation elongation factor EF1A, eukaryotic/archaeal]</t>
-  </si>
-  <si>
-    <t>purple</t>
-  </si>
-  <si>
-    <t>Ofaveolata002345</t>
-  </si>
-  <si>
-    <t>Acidified</t>
-  </si>
-  <si>
-    <t>salmon</t>
-  </si>
-  <si>
-    <t>Ofaveolata028911</t>
-  </si>
-  <si>
-    <t>IPR051302</t>
-  </si>
-  <si>
-    <t>NA [Dual serine/threonine and tyrosine protein kinase family]</t>
+    <t>Bleaching vs OA</t>
+  </si>
+  <si>
+    <t>Heat shock proteins</t>
+  </si>
+  <si>
+    <t>Ofaveolata021922</t>
+  </si>
+  <si>
+    <t>Suppression of tumorigenicity 13 (Hsp70 interacting protein)</t>
+  </si>
+  <si>
+    <t>Bleaching</t>
+  </si>
+  <si>
+    <t>OA</t>
+  </si>
+  <si>
+    <t>Ofaveolata023144</t>
+  </si>
+  <si>
+    <t>Ubiquitin homologues</t>
+  </si>
+  <si>
+    <t>Immune response</t>
+  </si>
+  <si>
+    <t>Ofaveolata000449</t>
+  </si>
+  <si>
+    <t>Lactose-binding lectin l-2-like</t>
+  </si>
+  <si>
+    <t>Ofaveolata017142</t>
+  </si>
+  <si>
+    <t>Galactose binding lectin domain</t>
+  </si>
+  <si>
+    <t>Oxidative stress/antioxidants</t>
+  </si>
+  <si>
+    <t>Ofaveolata000053</t>
+  </si>
+  <si>
+    <t>Protein-disulfide reductase (glutathione) activity</t>
+  </si>
+  <si>
+    <t>Ofaveolata008267</t>
+  </si>
+  <si>
+    <t>Peroxidase activity</t>
+  </si>
+  <si>
+    <t>Ofaveolata010796</t>
+  </si>
+  <si>
+    <t>Glutathione peroxidase activity</t>
+  </si>
+  <si>
+    <t>Ofaveolata024342</t>
+  </si>
+  <si>
+    <t>Animal haem peroxidase</t>
+  </si>
+  <si>
+    <t>OA + Bleaching vs OA</t>
+  </si>
+  <si>
+    <t>OA + Bleaching</t>
+  </si>
+  <si>
+    <t>Ofaveolata026158</t>
+  </si>
+  <si>
+    <t>Belongs to the glutathione peroxidase family</t>
   </si>
   <si>
     <t>Siderastrea siderea</t>
   </si>
   <si>
-    <t>Ssiderea055308</t>
-  </si>
-  <si>
-    <t>IPR050839</t>
-  </si>
-  <si>
-    <t>NA [Rho-associated serine/threonine kinase]</t>
-  </si>
-  <si>
-    <t>Ssiderea003902</t>
-  </si>
-  <si>
-    <t>IPR019585</t>
-  </si>
-  <si>
-    <t>NA [26S proteasome regulatory subunit Rpn7/COP9 signalosome complex subunit 1]</t>
-  </si>
-  <si>
-    <t>turquoise</t>
-  </si>
-  <si>
-    <t>Ssiderea000394</t>
-  </si>
-  <si>
-    <t>IPR024983</t>
-  </si>
-  <si>
-    <t>NA [Caspase HetF associated with Tprs (CHAT) domain]</t>
+    <t>Ssiderea001633</t>
+  </si>
+  <si>
+    <t>Protein folding in endoplasmic reticulum</t>
+  </si>
+  <si>
+    <t>Ssiderea058218</t>
+  </si>
+  <si>
+    <t>Cytochrome C oxidase</t>
   </si>
 </sst>
 </file>
@@ -227,20 +170,20 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -269,10 +212,10 @@
     <border>
       <left/>
       <right/>
-      <top style="thick">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -292,23 +235,25 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,19 +588,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA10580-7E3F-634F-8F24-78790B63446D}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DF9426-58E3-0B44-BD50-AE0C0558AE0F}">
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="84.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,242 +621,365 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3" t="s">
-        <v>53</v>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7" t="s">
-        <v>57</v>
+      <c r="D13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A13"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
